--- a/survey_templates/031_new_product_survey--survey_templates.xlsx
+++ b/survey_templates/031_new_product_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>product_survey_form</t>
+          <t>What is your product name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>survey_questions</t>
+          <t>What is your age group?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>product_survey_form</t>
+          <t>What type of product are you interested in purchasing?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>survey_questions</t>
+          <t>Which of the following features do you like most about the product?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,20 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>product_survey_form</t>
+          <t>How likely are you to recommend the product to a friend or family member?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>What is your contact email address? (leave blank if you don't have one)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>product_survey_form</t>
+          <t>Do you have any phone number to contact you?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Would you like to provide any additional comments or suggestions about the product?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Date of last purchase (if any)?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Time of last purchase?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>How did you find out about this product?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,312 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>How would you rate the product's performance?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>new_product_survey_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>product_survey_form</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>less_than_18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'option_1'}</t>
+          <t>Less than 18</t>
         </is>
       </c>
     </row>
@@ -1148,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'option_2'}</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -1165,182 +866,403 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'option_3'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>new_product_survey_page_4_choices</t>
+          <t>new_product_survey_page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'option_1'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>new_product_survey_page_4_choices</t>
+          <t>new_product_survey_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'option_2'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>new_product_survey_page_5_choices</t>
+          <t>new_product_survey_page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>55_or_older</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'option_1'}</t>
+          <t>55 or older</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>new_product_survey_page_5_choices</t>
+          <t>new_product_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>electronics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'option_2'}</t>
+          <t>Electronics</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>new_product_survey_page_7_choices</t>
+          <t>new_product_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>fashion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'option_1'}</t>
+          <t>Fashion</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>new_product_survey_page_7_choices</t>
+          <t>new_product_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>home_&amp;_kitchen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'option_2'}</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>new_product_survey_page_16_choices</t>
+          <t>new_product_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>outdoor_&amp;_sports</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'option_1'}</t>
+          <t>Outdoor &amp; Sports</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>new_product_survey_page_16_choices</t>
+          <t>new_product_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'option_2'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>new_product_survey_page_17_choices</t>
+          <t>new_product_survey_page_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'option_1'}</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>new_product_survey_page_17_choices</t>
+          <t>new_product_survey_page_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'option_2'}</t>
+          <t>Performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_4_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_4_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>brand_reputation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brand reputation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_5_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>not_at_all</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_5_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>somewhat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Somewhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_5_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>very_likely</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Very likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>online_advertisement</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Online advertisement</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Social media</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>word_of_mouth</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Word of mouth</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>in-store_promotion</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>In-store promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>new_product_survey_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
